--- a/docentes/Torres Sánchez José Luis - Estadisticos 20221.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -73,19 +73,19 @@
     <t>ESPINOSA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>LOYO</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>ALEXANDER</t>
   </si>
   <si>
-    <t>MARIO</t>
+    <t>DIEGO ARMANDO</t>
   </si>
 </sst>
 </file>
@@ -577,16 +577,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>81.25</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -600,16 +603,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>84.38</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -674,7 +680,7 @@
         <v>81.25</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,16 +697,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>81.25</v>
+        <v>84.38</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -710,7 +716,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -788,7 +794,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920159</v>
+        <v>21330051920164</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
@@ -806,29 +812,6 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920159</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Torres Sánchez José Luis - Estadisticos 20221.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
   <si>
     <t>Mat</t>
   </si>
@@ -68,24 +68,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
   </si>
 </sst>
 </file>
@@ -671,16 +653,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>81.25</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -697,16 +679,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -716,7 +698,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -746,75 +728,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920157</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920157</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920164</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
